--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:39:00+00:00</t>
+    <t>2026-06-22T13:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:09:12+00:00</t>
+    <t>2026-06-22T13:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:13:25+00:00</t>
+    <t>2026-06-22T13:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:33:44+00:00</t>
+    <t>2026-06-22T13:44:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:44:32+00:00</t>
+    <t>2026-06-22T13:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:47:42+00:00</t>
+    <t>2026-06-22T14:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:04:21+00:00</t>
+    <t>2026-06-22T14:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:24:08+00:00</t>
+    <t>2026-06-22T14:26:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:26:05+00:00</t>
+    <t>2026-06-22T14:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:28:00+00:00</t>
+    <t>2026-06-22T14:39:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:39:52+00:00</t>
+    <t>2026-06-29T10:03:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:03:57+00:00</t>
+    <t>2026-06-29T10:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:21:29+00:00</t>
+    <t>2026-06-29T10:25:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:25:23+00:00</t>
+    <t>2026-06-29T15:19:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:19:05+00:00</t>
+    <t>2026-07-20T14:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:29:12+00:00</t>
+    <t>2026-07-21T07:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T07:29:40+00:00</t>
+    <t>2026-07-21T07:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T07:54:03+00:00</t>
+    <t>2026-07-31T16:55:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T16:55:52+00:00</t>
+    <t>2026-08-03T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/nr-doc-core-immunization/ig/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:04:08+00:00</t>
+    <t>2026-08-04T12:14:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
